--- a/extenbooks/ES2302_extenbook.xlsx
+++ b/extenbooks/ES2302_extenbook.xlsx
@@ -2696,7 +2696,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A118"/>
+  <dimension ref="A1:A146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2749,7 +2749,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>**Status**: ingested</t>
+          <t>**Status**: study_complete</t>
         </is>
       </c>
     </row>
@@ -3342,7 +3342,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>## 6. Dual-axis emission</t>
+          <t>## 6. Conceptual continuity vs adjacent concepts</t>
         </is>
       </c>
     </row>
@@ -3352,26 +3352,210 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>The DPR mandates two distinct AnuData rows (level + percent-of-GDP).</t>
+          <t>The extension proxy `IMF WEO subject BCA (level) + BCA_NGDPD (% of GDP)</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Phase 5 enforces this in the loader: each WEO subject is tagged with</t>
+          <t>for country CHN` measures `China's current account balance` rather than</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>its own `subseries_id` (`ES2302-level` or `ES2302-pctgdp`) so the</t>
+          <t>`China's goods trade balance` or `China's BoP balance overall` because:</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
+        <is>
+          <t>- Source agency choice: Weber &amp; Shaikh (2020) Fig 2 explicitly cites IMF</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  WEO, not China State Administration of Foreign Exchange (SAFE) BoP</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  releases. WEO is the published recipe.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>- Methodology continuity: paper-window 1997-2017 values were WEO BCA /</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  BCA_NGDPD; extension years 2018-2024 use the *same* WEO subjects at</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  later vintages (semi-annual April + October publication).</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>- Disambiguation: current account (BCA) ≠ goods trade balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  (ES2301 / Census FT900): BCA adds services, primary income, and</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  secondary income to the goods balance. % of GDP normalization</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  (BCA_NGDPD) differs from level (BCA): the figure plots both on</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  a dual y-axis because the units are not commensurable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>The book's original concept (Weber &amp; Shaikh 2020 p. 432, citing Fig 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>was: China's CA surplus "peaks at about 10% of GDP in 2007, then falls</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>sharply to about 1.3% by 2017" — the reversal narrative that</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>counter-evidences the currency-manipulation hypothesis. The modern series</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>preserves the WEO BCA concept and the dual unit emission (level + %GDP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>while permitting WEO vintage revisions to shift historical values</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>0.1-0.5 percentage points. This is NOT a proxy substitution forbidden</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>by the No-Proxy rule because IMF WEO is exactly the source the paper</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>cites; we pull the same two subjects (BCA, BCA_NGDPD) for the same</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>country (CHN) at a later vintage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>## 7. Dual-axis emission</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>The DPR mandates two distinct AnuData rows (level + percent-of-GDP).</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Phase 5 enforces this in the loader: each WEO subject is tagged with</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>its own `subseries_id` (`ES2302-level` or `ES2302-pctgdp`) so the</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
         <is>
           <t>chopped CSV and extenbook reflect the unit split.</t>
         </is>
@@ -3736,11 +3920,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3763,54 +3947,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>phases_completed</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>[5, 6, 7]</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>artifacts</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>{"dpr": "Technical/docs/series/ES2302_DPR.md", "epr": "Technical/docs/series/ES2302_EPR.md", "loader": "Technical/code/L01_loaders/L01_ES2302_load.py", "processor": "Technical/code/P02_processors/P02_ES2302_construct.py", "validator": "Technical/code/V03_validators/V03_ES2302_validate.py"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>last_updated</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>author</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>opus-fanout-ES</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
